--- a/MurrayTools.tab/Utilities.panel/ProjectUtilities.Stack/Exports.pulldown/GenerateBulkBOM.pushbutton/MR-BOM.xlsx
+++ b/MurrayTools.tab/Utilities.panel/ProjectUtilities.Stack/Exports.pulldown/GenerateBulkBOM.pushbutton/MR-BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Egnyte\Shared\BIM\Murray CADetailing Dept\REVIT\MURRAY RIBBON\Murray.extension\MurrayTools.tab\Utilities.panel\ProjectUtilities.Stack\Exports.pulldown\GenerateBulkBOM.pushbutton\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4BC193-4AB1-4689-A64D-62EFA67BD566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5616BDA3-DD21-4F48-8BF2-18EEF87BDE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{3AEB8DE0-985F-4A48-8335-FFD4EE2C061B}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{3AEB8DE0-985F-4A48-8335-FFD4EE2C061B}"/>
   </bookViews>
   <sheets>
     <sheet name="MEP Fabrication Pipe BOM" sheetId="1" r:id="rId1"/>
@@ -642,36 +642,37 @@
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1163,12 +1164,12 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="10" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="40.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="9" customWidth="1"/>
-    <col min="6" max="7" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="7" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1178,7 +1179,7 @@
       <c r="B1" s="30"/>
       <c r="C1" s="31"/>
       <c r="D1" s="32"/>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="25"/>
@@ -1207,7 +1208,7 @@
       <c r="B4" s="34"/>
       <c r="C4" s="34"/>
       <c r="D4" s="35"/>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="11"/>
@@ -1240,12 +1241,12 @@
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
       <c r="D7" s="35"/>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="7" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="41">
         <f ca="1">NOW()</f>
-        <v>45779.276452199076</v>
+        <v>45797.43305659722</v>
       </c>
       <c r="G7" s="42"/>
     </row>
@@ -1254,7 +1255,7 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="11"/>
@@ -1265,7 +1266,7 @@
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="27"/>
@@ -1276,7 +1277,7 @@
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="15"/>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F10" s="11"/>
@@ -1287,7 +1288,7 @@
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="15"/>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="7" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="11"/>
@@ -1300,7 +1301,7 @@
       <c r="B12" s="25"/>
       <c r="C12" s="25"/>
       <c r="D12" s="26"/>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="11"/>
@@ -1312,10 +1313,10 @@
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="20"/>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="11"/>
@@ -1327,10 +1328,10 @@
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="23"/>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="11"/>
@@ -1343,37 +1344,37 @@
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="15"/>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
+      <c r="A34" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="24">
